--- a/North As-Built Tracker.xlsx
+++ b/North As-Built Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\As-Built\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasaan.shafeeq\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEA94E9-8700-4784-812C-A329D70C6735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BBA964-3E4A-4795-BF01-0001139DA5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distribution" sheetId="1" r:id="rId1"/>
@@ -37,19 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
-  <si>
-    <t>Sr.no</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Total Scope KM</t>
-  </si>
-  <si>
-    <t>As-builts received</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
   <si>
     <t>Percentage of Work Completed</t>
   </si>
@@ -60,45 +48,24 @@
     <t>Bahria Ph 7 POP Ring Project</t>
   </si>
   <si>
-    <t>6 KM</t>
-  </si>
-  <si>
     <t>Updated</t>
   </si>
   <si>
     <t>DHA -CSC POP to Bahria  8 POP Via Sereen City (BH 7)</t>
   </si>
   <si>
-    <t>11 km</t>
-  </si>
-  <si>
-    <t>11 KM</t>
-  </si>
-  <si>
     <t>Railway Back Haul</t>
   </si>
   <si>
-    <t>52 km</t>
-  </si>
-  <si>
-    <t>16 km</t>
-  </si>
-  <si>
     <t>Not Updated</t>
   </si>
   <si>
     <t>H-13</t>
   </si>
   <si>
-    <t>10 KM</t>
-  </si>
-  <si>
     <t>New Blue Area</t>
   </si>
   <si>
-    <t>14 KM</t>
-  </si>
-  <si>
     <t>Total Scope DC</t>
   </si>
   <si>
@@ -172,6 +139,36 @@
   </si>
   <si>
     <t>I-8/4</t>
+  </si>
+  <si>
+    <t>As-builts Received</t>
+  </si>
+  <si>
+    <t>Total Scope (km)</t>
+  </si>
+  <si>
+    <t>6 (km)</t>
+  </si>
+  <si>
+    <t>11 (km)</t>
+  </si>
+  <si>
+    <t>16 (km)</t>
+  </si>
+  <si>
+    <t>10 (km)</t>
+  </si>
+  <si>
+    <t>14 (km)</t>
+  </si>
+  <si>
+    <t>52 (km)</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Sr.#</t>
   </si>
 </sst>
 </file>
@@ -577,22 +574,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -600,20 +597,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="str">
         <f>ROUND(VALUE(LEFT(D2,FIND(" ",D2)-1))/VALUE(LEFT(C2,FIND(" ",C2)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -621,20 +618,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="str">
         <f>ROUND(VALUE(LEFT(D3,FIND(" ",D3)-1))/VALUE(LEFT(C3,FIND(" ",C3)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -642,20 +639,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="str">
-        <f t="shared" ref="E2:E13" si="0">ROUND(VALUE(LEFT(D4,FIND(" ",D4)-1))/VALUE(LEFT(C4,FIND(" ",C4)-1))*100,0)&amp;"%"</f>
+        <f t="shared" ref="E4:E13" si="0">ROUND(VALUE(LEFT(D4,FIND(" ",D4)-1))/VALUE(LEFT(C4,FIND(" ",C4)-1))*100,0)&amp;"%"</f>
         <v>0%</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -663,20 +660,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>73%</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -684,20 +681,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30%</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -705,20 +702,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0%</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -726,20 +723,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0%</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -747,20 +744,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>41%</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -768,20 +765,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0%</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -789,20 +786,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>100%</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -810,20 +807,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>100%</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -831,20 +828,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0%</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -858,29 +855,32 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.1796875" customWidth="1"/>
+    <col min="1" max="1" width="6.08984375" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="20.36328125" customWidth="1"/>
     <col min="6" max="6" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -888,20 +888,20 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E2" s="5" t="str">
         <f>ROUND(VALUE(LEFT(D2,FIND(" ",D2)-1))/VALUE(LEFT(C2,FIND(" ",C2)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -909,20 +909,20 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E3" s="5" t="str">
         <f t="shared" ref="E3:E6" si="0">ROUND(VALUE(LEFT(D3,FIND(" ",D3)-1))/VALUE(LEFT(C3,FIND(" ",C3)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -930,20 +930,20 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E4" s="5" t="str">
         <f t="shared" si="0"/>
         <v>31%</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -951,20 +951,20 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>100%</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -972,20 +972,20 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>100%</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/North As-Built Tracker.xlsx
+++ b/North As-Built Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasaan.shafeeq\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BBA964-3E4A-4795-BF01-0001139DA5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E08D99-A70D-4323-ABBA-CFA6AA2A61F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distribution" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
   <si>
     <t>Percentage of Work Completed</t>
   </si>
@@ -108,12 +108,6 @@
     <t>10 DC</t>
   </si>
   <si>
-    <t xml:space="preserve">Overses 3 Phase 8 </t>
-  </si>
-  <si>
-    <t>Overses7 Phase 8</t>
-  </si>
-  <si>
     <t>8 DC</t>
   </si>
   <si>
@@ -123,9 +117,6 @@
     <t>51 DC</t>
   </si>
   <si>
-    <t>21 DC</t>
-  </si>
-  <si>
     <t>PWD</t>
   </si>
   <si>
@@ -169,6 +160,21 @@
   </si>
   <si>
     <t>Sr.#</t>
+  </si>
+  <si>
+    <t>Sr #</t>
+  </si>
+  <si>
+    <t>I-10/1</t>
+  </si>
+  <si>
+    <t>12 DC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BahriaPhase 8 Overses 3  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahria Phase 8 Overses7 </t>
   </si>
 </sst>
 </file>
@@ -251,16 +257,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,9 +582,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="3.36328125" customWidth="1"/>
     <col min="2" max="2" width="25.7265625" customWidth="1"/>
     <col min="3" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="31.54296875" customWidth="1"/>
@@ -574,273 +594,294 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="str">
+      <c r="E2" s="5" t="str">
         <f>ROUND(VALUE(LEFT(D2,FIND(" ",D2)-1))/VALUE(LEFT(C2,FIND(" ",C2)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="str">
+      <c r="E3" s="5" t="str">
         <f>ROUND(VALUE(LEFT(D3,FIND(" ",D3)-1))/VALUE(LEFT(C3,FIND(" ",C3)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="5" t="str">
+        <f t="shared" ref="E4:E14" si="0">ROUND(VALUE(LEFT(D4,FIND(" ",D4)-1))/VALUE(LEFT(C4,FIND(" ",C4)-1))*100,0)&amp;"%"</f>
+        <v>55%</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>73%</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>30%</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" ref="E4:E13" si="0">ROUND(VALUE(LEFT(D4,FIND(" ",D4)-1))/VALUE(LEFT(C4,FIND(" ",C4)-1))*100,0)&amp;"%"</f>
+      <c r="E7" s="5" t="str">
+        <f t="shared" si="0"/>
         <v>0%</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>73%</v>
-      </c>
-      <c r="F5" s="1" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0%</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>30%</v>
-      </c>
-      <c r="F6" s="1" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>45%</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0%</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>100%</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0%</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="str">
+      <c r="E14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>0%</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>0%</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>41%</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>0%</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>100%</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>100%</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>0%</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="F14" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -855,136 +896,136 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" customWidth="1"/>
-    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="20.36328125" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="1" max="1" width="3.90625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.36328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="5" t="str">
+      <c r="C2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="7" t="str">
         <f>ROUND(VALUE(LEFT(D2,FIND(" ",D2)-1))/VALUE(LEFT(C2,FIND(" ",C2)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="5" t="str">
+      <c r="C3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="7" t="str">
         <f t="shared" ref="E3:E6" si="0">ROUND(VALUE(LEFT(D3,FIND(" ",D3)-1))/VALUE(LEFT(C3,FIND(" ",C3)-1))*100,0)&amp;"%"</f>
         <v>100%</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="5" t="str">
+      <c r="D4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>31%</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="5" t="str">
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>100%</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="5" t="str">
+      <c r="C6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>100%</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
